--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TBV</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0304998358-056</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>553704.0</v>
+        <v>1002777.78</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>44296.0</v>
+        <v>80222.22</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>598000.0</v>
+        <v>1083000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -403,61 +403,57 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>077168002321</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>HỘ KINH DOANH NHÀ SÁCH ĐÔNG HẢI</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>32-34-36-38 Lý Thường Kiệt, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>905774.0</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>72462.0</v>
-      </c>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>978236.0</v>
+        <v>875000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +487,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TSV</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>3500728882</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN LONG QUÂN</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Số 407-409-411 Thống Nhất, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>8000000.0</v>
+        <v>3337000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>640000.0</v>
+        <v>272110.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>8640000.0</v>
+        <v>3609110.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -558,170 +554,6 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>C25TKT</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>02/10/2025</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>3502219376</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>1.476E7</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>738000.0</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="n">
-        <v>1.5498E7</v>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>C25TYY</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>06/10/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>3703355241</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>3.2414E7</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>2593120.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="n">
-        <v>3.500712E7</v>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBV</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304998358-056</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1002777.78</v>
+        <v>553704.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>80222.22</v>
+        <v>44296.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1083000.0</v>
+        <v>598000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -403,57 +403,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>45993</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>077168002321</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NHÀ SÁCH ĐÔNG HẢI</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>32-34-36-38 Lý Thường Kiệt, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1393519.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>111481.0</v>
+      </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>875000.0</v>
+        <v>1505000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -487,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500728882</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN LONG QUÂN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 407-409-411 Thống Nhất, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502217971</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>3337000.0</v>
+        <v>905774.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>272110.0</v>
+        <v>72462.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>3609110.0</v>
+        <v>978236.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -554,6 +558,419 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TSV</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3500898348</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>8000000.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>640000.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>8640000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25TKT</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502219376</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>1.476E7</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>738000.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>1.5498E7</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TTT</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>9140</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502252817</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>699999.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>56000.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>755999.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3703355241</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>3.2414E7</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>2593120.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>3.500712E7</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3703355241</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>8.405E7</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>6724000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>9.0774E7</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>553704.0</v>
+        <v>4566600.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>44296.0</v>
+        <v>365328.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>598000.0</v>
+        <v>4931928.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1393519.0</v>
+        <v>4277778.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>111481.0</v>
+        <v>342222.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1505000.0</v>
+        <v>4620000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>3502420437</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>905774.0</v>
+        <v>541667.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>72462.0</v>
+        <v>43333.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>978236.0</v>
+        <v>585000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,12 +574,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TSV</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -589,41 +589,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>8000000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>640000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>8640000.0</v>
+        <v>3150000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,54 +657,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TKT</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>366</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502219376</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1.476E7</v>
+        <v>1814000.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>738000.0</v>
-      </c>
-      <c r="M11" s="13"/>
+        <v>90700.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1.5498E7</v>
+        <v>1904700.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -738,56 +740,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>371</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>699999.0</v>
+        <v>4350000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>56000.0</v>
+        <v>217500.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>755999.0</v>
+        <v>4567500.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -821,56 +823,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>373</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3703355241</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>3.2414E7</v>
+        <v>4000000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>2593120.0</v>
+        <v>200000.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>3.500712E7</v>
+        <v>4200000.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -904,56 +906,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>375</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3703355241</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>8.405E7</v>
+        <v>4300000.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>6724000.0</v>
+        <v>215000.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>9.0774E7</v>
+        <v>4515000.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -971,6 +973,255 @@
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>4678</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>2210000.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>160000.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>2370000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>623148.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>49852.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>673000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>2422540.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>193803.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>2616343.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -989,32 +989,32 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>377</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1028,17 +1028,17 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>2210000.0</v>
+        <v>4550000.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>160000.0</v>
+        <v>227500.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>2370000.0</v>
+        <v>4777500.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1072,32 +1072,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>385</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1111,17 +1111,17 @@
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>623148.0</v>
+        <v>4100000.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>49852.0</v>
+        <v>205000.0</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>673000.0</v>
+        <v>4305000.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TMQ</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502479416</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1194,34 +1194,200 @@
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>2422540.0</v>
+        <v>2210000.0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>193803.0</v>
+        <v>160000.0</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
+        <v>2370000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>623148.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>49852.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>673000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>2422540.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>193803.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
         <v>2616343.0</v>
       </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBR</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316158113</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4566600.0</v>
+        <v>553704.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>365328.0</v>
+        <v>44296.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>4931928.0</v>
+        <v>598000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>45993</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>4277778.0</v>
+        <v>1393519.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>342222.0</v>
+        <v>111481.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4620000.0</v>
+        <v>1505000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502420437</t>
+          <t>3500805921</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>541667.0</v>
+        <v>905774.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>43333.0</v>
+        <v>72462.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>585000.0</v>
+        <v>978236.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,12 +574,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TSV</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -589,41 +589,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3500898348</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>3000000.0</v>
+        <v>8000000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>150000.0</v>
+        <v>640000.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>3150000.0</v>
+        <v>8640000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +657,54 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TKT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3502219376</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1814000.0</v>
+        <v>1.476E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>90700.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>738000.0</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1904700.0</v>
+        <v>1.5498E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,56 +738,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>4350000.0</v>
+        <v>699999.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>217500.0</v>
+        <v>56000.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>4567500.0</v>
+        <v>755999.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,56 +821,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3703355241</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>4000000.0</v>
+        <v>3.2414E7</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>200000.0</v>
+        <v>2593120.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>4200000.0</v>
+        <v>3.500712E7</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -906,56 +904,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3703355241</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>4300000.0</v>
+        <v>8.405E7</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>215000.0</v>
+        <v>6724000.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>4515000.0</v>
+        <v>9.0774E7</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -973,421 +971,6 @@
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>C25TBP</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>21/10/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>3502431414</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>4550000.0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>227500.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13" t="n">
-        <v>4777500.0</v>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>C25TBP</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>23/10/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>3502431414</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>4100000.0</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>205000.0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13" t="n">
-        <v>4305000.0</v>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>C25TMQ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>4678</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>17/10/2025</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>3502479416</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>2210000.0</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>160000.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="n">
-        <v>2370000.0</v>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>C25THP</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>1779</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>16/10/2025</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>3502550066</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>623148.0</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>49852.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13" t="n">
-        <v>673000.0</v>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>C25THP</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>17/10/2025</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>3502550066</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>2422540.0</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>193803.0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13" t="n">
-        <v>2616343.0</v>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TNA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>792</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0304447047</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH SƠN VÀ CHỐNG THẤM NAM VIỆT</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>54 Đường S9, Phường Tây Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>553704.0</v>
+        <v>2.0397222E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>44296.0</v>
+        <v>1631778.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>598000.0</v>
+        <v>2.2029E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0317094085</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG AKACO</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>B12/24M đường Cây Bàng, ấp 2, Xã Tân Nhựt, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1393519.0</v>
+        <v>1.35913246E8</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>111481.0</v>
+        <v>1.087306E7</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1505000.0</v>
+        <v>1.46786306E8</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>0317094085</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG AKACO</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>B12/24M đường Cây Bàng, ấp 2, Xã Tân Nhựt, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>905774.0</v>
+        <v>1.43545772E8</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>72462.0</v>
+        <v>1.1483662E7</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>978236.0</v>
+        <v>1.55029434E8</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,12 +574,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TSV</t>
+          <t>C25TQT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>23795</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -589,41 +589,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500898348</t>
+          <t>3500678864</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>8000000.0</v>
+        <v>5132400.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>640000.0</v>
+        <v>410592.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>8640000.0</v>
+        <v>5542992.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TKT</t>
+          <t>C25TQT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -672,39 +672,41 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502219376</t>
+          <t>3500678864</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1.476E7</v>
+        <v>7050680.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>738000.0</v>
-      </c>
-      <c r="M11" s="13"/>
+        <v>564054.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1.5498E7</v>
+        <v>7614734.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -738,56 +740,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TQT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3500678864</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>699999.0</v>
+        <v>2293200.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>56000.0</v>
+        <v>183456.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>755999.0</v>
+        <v>2476656.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -821,56 +823,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TQT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3703355241</t>
+          <t>3500678864</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>3.2414E7</v>
+        <v>1.67643E7</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>2593120.0</v>
+        <v>1341144.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>3.500712E7</v>
+        <v>1.8105444E7</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -904,56 +906,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TQT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3703355241</t>
+          <t>3500678864</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÔI TRƯỜNG HẠNH NHẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 42/2 Khu phố Bình Quới B, Bình Chuẩn 45, Phường Thuận Giao, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3500779171</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>8.405E7</v>
+        <v>3188640.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>6724000.0</v>
+        <v>255091.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>9.0774E7</v>
+        <v>3443731.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -971,6 +973,1002 @@
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1.78708E7</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1429664.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1.9300464E7</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>25597</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>8187270.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>654982.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>8842252.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>25952</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>1.592227E7</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>1273782.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>1.7196052E7</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>26633</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>1.721811E7</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>1377449.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>1.8595559E7</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>26639</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1.508871E7</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1207097.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>1.6295807E7</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>27172</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>1.614964E7</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>1291971.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>1.7441611E7</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>27532</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>9181600.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>734528.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>9916128.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>27534</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>6279000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>502320.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>6781320.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>27660</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>27670</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>1.2987E7</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>1038960.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>1.402596E7</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>27892</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>7.119106E7</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>5695285.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>7.6886345E7</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TQT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>28439</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3500779171</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>1.07599912E8</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>8607993.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>1.16207905E8</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TNA</t>
+          <t>C25TCK</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304447047</t>
+          <t>0316407289</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SƠN VÀ CHỐNG THẤM NAM VIỆT</t>
+          <t>CÔNG TY TNHH ZEUS TECHNOLOGY</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>54 Đường S9, Phường Tây Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 2, Số 21 Đường Võ Trường Toản, Phường An Khánh, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>2.0397222E7</v>
+        <v>1.28E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1631778.0</v>
+        <v>1024000.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>2.2029E7</v>
+        <v>1.3824E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TCK</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>93506</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0317094085</t>
+          <t>0316407289</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG AKACO</t>
+          <t>CÔNG TY TNHH ZEUS TECHNOLOGY</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>B12/24M đường Cây Bàng, ấp 2, Xã Tân Nhựt, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 2, Số 21 Đường Võ Trường Toản, Phường An Khánh, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1.35913246E8</v>
+        <v>9666666.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1.087306E7</v>
+        <v>773334.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1.46786306E8</v>
+        <v>1.044E7</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,12 +491,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TCK</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>93513</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -506,41 +506,41 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0317094085</t>
+          <t>0316407289</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIẢI PHÁP XÂY DỰNG AKACO</t>
+          <t>CÔNG TY TNHH ZEUS TECHNOLOGY</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>B12/24M đường Cây Bàng, ấp 2, Xã Tân Nhựt, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 2, Số 21 Đường Võ Trường Toản, Phường An Khánh, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1.43545772E8</v>
+        <v>0.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1.1483662E7</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>1.55029434E8</v>
+        <v>0.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,56 +574,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TCK</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>23795</t>
+          <t>93566</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>0316407289</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ZEUS TECHNOLOGY</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 2, Số 21 Đường Võ Trường Toản, Phường An Khánh, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>5132400.0</v>
+        <v>7466148.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>410592.0</v>
+        <v>597292.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>0.0</v>
+        <v>519037.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>5542992.0</v>
+        <v>8063440.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +657,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>12420</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>7050680.0</v>
+        <v>2.0185185E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>564054.0</v>
+        <v>1614815.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>7614734.0</v>
+        <v>2.18E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,56 +740,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>2293200.0</v>
+        <v>1.0338889E7</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>183456.0</v>
+        <v>827111.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>2476656.0</v>
+        <v>1.1166E7</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,56 +823,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1.67643E7</v>
+        <v>4.0435185E7</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1341144.0</v>
+        <v>3234815.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>1.8105444E7</v>
+        <v>4.367E7</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -906,56 +906,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>32591</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>3188640.0</v>
+        <v>1.6574074E7</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>255091.0</v>
+        <v>1325926.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>3443731.0</v>
+        <v>1.79E7</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -989,56 +989,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1.78708E7</v>
+        <v>1.6574074E7</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1429664.0</v>
+        <v>1325926.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>1.9300464E7</v>
+        <v>1.79E7</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1072,56 +1072,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>8187270.0</v>
+        <v>5.9618182E7</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>654982.0</v>
+        <v>5961818.0</v>
       </c>
       <c r="M16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>8842252.0</v>
+        <v>6.558E7</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1155,56 +1155,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>1.592227E7</v>
+        <v>5.0763636E7</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1273782.0</v>
+        <v>5076364.0</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>1.7196052E7</v>
+        <v>5.584E7</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1238,56 +1238,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>1.721811E7</v>
+        <v>6.4363636E7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>1377449.0</v>
+        <v>6436364.0</v>
       </c>
       <c r="M18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>1.8595559E7</v>
+        <v>7.08E7</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1321,56 +1321,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THM</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>25/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3500636705</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH HOẠ MY</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>114 Lý Thường Kiệt, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1.508871E7</v>
+        <v>7.7164545E7</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1207097.0</v>
+        <v>7716455.0</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>1.6295807E7</v>
+        <v>8.4881E7</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1404,56 +1404,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>1.614964E7</v>
+        <v>1.0124075E7</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>1291971.0</v>
+        <v>809926.0</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>1.7441611E7</v>
+        <v>1.0934001E7</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1487,56 +1487,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>9181600.0</v>
+        <v>2.0772223E7</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>734528.0</v>
+        <v>1661778.0</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>9916128.0</v>
+        <v>2.2434001E7</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1570,56 +1570,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>6279000.0</v>
+        <v>1.071389E7</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>502320.0</v>
+        <v>857110.0</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>6781320.0</v>
+        <v>1.1571E7</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1653,56 +1653,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>18/10/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0.0</v>
+        <v>1.2244445E7</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0.0</v>
+        <v>979556.0</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>0.0</v>
+        <v>1.3224001E7</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1736,56 +1736,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>1.2987E7</v>
+        <v>1.6433334E7</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>1038960.0</v>
+        <v>1314667.0</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>1.402596E7</v>
+        <v>1.7748001E7</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1819,56 +1819,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THN</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>7.119106E7</v>
+        <v>2.6033333E7</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>5695285.0</v>
+        <v>2082667.0</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>7.6886345E7</v>
+        <v>2.8116E7</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1902,56 +1902,56 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25TQT</t>
+          <t>C25THN</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3500678864</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Số 39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3500779171</t>
+          <t>3502501171</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG ĐẠI THÀNH CÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>1.07599912E8</v>
+        <v>3.5235185E7</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>8607993.0</v>
+        <v>2818815.0</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>1.16207905E8</v>
+        <v>3.8054E7</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1969,6 +1969,1832 @@
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25THN</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>3361</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>2.94E7</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>2352000.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>3.1752E7</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25THN</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>3.5274074E7</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>2821926.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>3.8096E7</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25THN</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>2.7066668E7</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>2165333.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>2.9232001E7</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502356936</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN KỸ THUẬT NHẤT TÂM</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>548B Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>8063000.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>645040.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>8708040.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TSP</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502359239</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH TRÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Bến Chương Dương, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>4.6296296E7</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>3703704.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>5.0E7</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TSP</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502359239</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH TRÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Bến Chương Dương, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>1.71296297E8</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>1.3703703E7</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>1.85E8</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TSP</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502359239</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH TRÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 56 Bến Chương Dương, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>1.88853703E8</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1.5108297E7</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>2.03962E8</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>66406</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>1.34566272E8</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>1.0765302E7</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>1.45331574E8</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>66775</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1.23730164E8</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>9898413.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>1.33628577E8</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>67328</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>1.38224676E8</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>1.1057974E7</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>1.4928265E8</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>67849</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1.41575526E8</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>1.1326042E7</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>1.52901568E8</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>68412</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>9.8077728E7</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>7846218.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>4.36275E7</v>
+      </c>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>1.05923946E8</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>68698</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>3.1189176E8</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>2.4951341E7</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>3.36843101E8</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>68715</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>1.251648E8</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>1.0013184E7</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>1.35177984E8</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>69015</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>1.41705228E8</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1.1336418E7</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>1.53041646E8</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>69302</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>1.41636033E8</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1.1330883E7</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>1.52966916E8</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>69571</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1.2290472E8</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>9832378.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>1.32737098E8</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>70542</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>1.36029732E8</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>1.0882379E7</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>1.46912111E8</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>70811</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>1.37039352E8</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>1.0963148E7</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>1.480025E8</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>71078</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>1.42794066E8</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>1.1423525E7</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>1.54217591E8</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>72577</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>9.8342064E7</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>7867365.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>1.06209429E8</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>72994</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3701760678</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ NUM BER ONE</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>219 Đại lộ Bình Dương, Phường Lái Thiêu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502501171</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI PHÁT ĐẠT  VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>1408950.0</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>112716.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>1521666.0</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316066744</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG DỊCH VỤ LÂM PHƯƠNG</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>18E3 Chu Văn An, Phường Bình Thạnh, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4.87592593E8</v>
+        <v>4566600.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3.9007407E7</v>
+        <v>365328.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>5.266E8</v>
+        <v>4931928.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TBT</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3501772161</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÊ TÔNG VÀ XÂY LẮP HODECO</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Thôn 9 Gò Găng, Xã Long Sơn, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>9777778.0</v>
+        <v>4566600.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>782222.0</v>
+        <v>365328.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1.056E7</v>
+        <v>4931928.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -475,6 +475,1575 @@
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25TDL</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>54140</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>4277778.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>342222.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TDL</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>68587</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>4231482.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>338518.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>46296.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>4570000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>11440</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>541667.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>43333.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>585000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>150000.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>3150000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>1814000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>90700.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>1904700.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>4350000.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>217500.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>4567500.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>4000000.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>4200000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>4300000.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>215000.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>4515000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>4100000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>205000.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>4305000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>2100000.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>105000.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>2205000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>4429080.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>221454.0</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4650534.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>4619430.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>230972.0</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>4850402.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>29/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>4333500.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>216675.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4550175.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>4678</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>2210000.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>160000.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>2370000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>623148.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>49852.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>673000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>2422540.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>193803.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>2616343.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>2422574.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>193806.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>2616380.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TLN</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3602750365</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CỒN - LÊ NGUYỄN</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>A2/189 B, KP 2, Phường Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>4254640.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>340371.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4595011.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/10/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBR</t>
+          <t>C25TKO</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316158113</t>
+          <t>0104359717</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
+          <t>CÔNG TY CỔ PHẦN CÔNG NGHỆ KIOTVIET</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 6-7, số 1B Yết Kiêu, Phường Cửa Nam, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4566600.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>365328.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>4931928.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,54 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TBR</t>
+          <t>C25TPM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>146387</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0316158113</t>
+          <t>0104359717</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
+          <t>CÔNG TY CỔ PHẦN CÔNG NGHỆ KIOTVIET</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 6-7, số 1B Yết Kiêu, Phường Cửa Nam, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>4566600.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>365328.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4931928.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -471,7 +469,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -491,56 +489,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25TCL</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>0304995011-005</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>Chi Nhánh Công Ty TNHH Dịch Vụ Tiếp Vận Toàn Cầu Tại Nghệ An</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường Nam Cấm Cửa Lò, Xóm Hợp Tiến , Xã Đông Lộc, Tỉnh Nghệ An, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4277778.0</v>
+        <v>1.5188889E7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>342222.0</v>
+        <v>1215111.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>4620000.0</v>
+        <v>1.6404E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,12 +572,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25TCL</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -589,41 +587,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>0304995011-005</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>Chi Nhánh Công Ty TNHH Dịch Vụ Tiếp Vận Toàn Cầu Tại Nghệ An</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường Nam Cấm Cửa Lò, Xóm Hợp Tiến , Xã Đông Lộc, Tỉnh Nghệ An, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>4231482.0</v>
+        <v>1.5188889E7</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>338518.0</v>
+        <v>1215111.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>46296.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>4570000.0</v>
+        <v>1.6404E7</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +655,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25THH</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502420437</t>
+          <t>0305544639</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỒNG HUẾ</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>26C Phan Đăng Lưu, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>541667.0</v>
+        <v>4.218991E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>43333.0</v>
+        <v>3375193.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>585000.0</v>
+        <v>4.5565103E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,56 +738,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0308649502</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XUẤT NHẬP KHẨU CƯỜNG PHÁT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>48 Tân Chánh Hiệp 03, Phường Trung Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>3000000.0</v>
+        <v>3.3346667E7</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>150000.0</v>
+        <v>2667733.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>3150000.0</v>
+        <v>3.60144E7</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,56 +821,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0311842753</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH GẠCH THUẬN THÀNH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>24C Hồ Học Lãm, Phường Phú Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1814000.0</v>
+        <v>369208.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>90700.0</v>
+        <v>29537.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>1904700.0</v>
+        <v>398745.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -906,56 +904,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0311842753</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH GẠCH THUẬN THÀNH</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>24C Hồ Học Lãm, Phường Phú Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>4350000.0</v>
+        <v>4444480.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>217500.0</v>
+        <v>355558.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>4567500.0</v>
+        <v>4800038.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -989,12 +987,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1004,41 +1002,41 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0312512557</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>Công ty cổ phần Viet Tiles</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>17 Đường số 40, Khu phố 27, Phường An Khánh, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>4000000.0</v>
+        <v>1564815.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>200000.0</v>
+        <v>125185.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>4200000.0</v>
+        <v>1690000.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1072,56 +1070,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TKM</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>441</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0317566443</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN MASFICO VIỆT NAM</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>25 Đường 109, Khu phố 5, Phường Phước Long, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>4300000.0</v>
+        <v>2961600.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>215000.0</v>
+        <v>236928.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0.0</v>
+        <v>1198400.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>4515000.0</v>
+        <v>3198528.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1155,56 +1153,54 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTM</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>1100869003</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI ĐỒNG TÂM</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 7, Khu phố 6, xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công Ty TNHH Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>4550000.0</v>
+        <v>150926.0</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>227500.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>12074.0</v>
+      </c>
+      <c r="M17" s="13"/>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>4777500.0</v>
+        <v>163000.0</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1238,56 +1234,54 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTM</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>1100869003</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI ĐỒNG TÂM</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 7, Khu phố 6, xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công Ty TNHH Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>4100000.0</v>
+        <v>1.07676E7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>205000.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>861408.0</v>
+      </c>
+      <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>4305000.0</v>
+        <v>1.1629008E7</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1321,56 +1315,54 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTM</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>1100869003</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI ĐỒNG TÂM</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 7, Khu phố 6, xã Bến Lức, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công Ty TNHH Đông Dương Vũng Tàu</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>2100000.0</v>
+        <v>2.1818213E7</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>105000.0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1745457.0</v>
+      </c>
+      <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>2205000.0</v>
+        <v>2.356367E7</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1404,54 +1396,54 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25TCH</t>
+          <t>C25TTQ</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3502470942</t>
+          <t>2901204820</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+          <t>CÔNG TY TNHH THANH QUYỀN</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Nhà bà Thanh, xóm Thọ Sơn - xã Quỳ Hợp - tỉnh Nghệ An.</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>4429080.0</v>
+        <v>3.0E7</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>221454.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>4650534.0</v>
+        <v>3.3E7</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1485,54 +1477,54 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25TCH</t>
+          <t>C25TTQ</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3502470942</t>
+          <t>2901204820</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+          <t>CÔNG TY TNHH THANH QUYỀN</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Nhà bà Thanh, xóm Thọ Sơn - xã Quỳ Hợp - tỉnh Nghệ An.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>4619430.0</v>
+        <v>3.0E7</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>230972.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>4850402.0</v>
+        <v>3.3E7</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1566,54 +1558,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25TCH</t>
+          <t>C25TSV</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3502470942</t>
+          <t>3500898348</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>4333500.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>216675.0</v>
-      </c>
-      <c r="M22" s="13"/>
+        <v>240000.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>4550175.0</v>
+        <v>3240000.0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1647,56 +1641,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>3501454948</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>CÔNG TY TNHH PHÚ GIA KHANG</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 8, Thôn Sông Cầu, Xã Nghĩa Thành, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>2210000.0</v>
+        <v>9.2592593E7</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>160000.0</v>
+        <v>7407407.0</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>2370000.0</v>
+        <v>1.0E8</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1730,56 +1724,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TTL</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>539</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502360474</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THANH LONG VŨNG TÀU</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>28A1 Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>623148.0</v>
+        <v>9.272E7</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>49852.0</v>
+        <v>7417600.0</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>673000.0</v>
+        <v>1.001376E8</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1813,56 +1807,54 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TSN</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502425026</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>2422540.0</v>
+        <v>1.658E7</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>193803.0</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1326400.0</v>
+      </c>
+      <c r="M25" s="13"/>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>2616343.0</v>
+        <v>1.79064E7</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1896,56 +1888,54 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TSN</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>913</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502425026</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>2422574.0</v>
+        <v>5646673.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>193806.0</v>
-      </c>
-      <c r="M26" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>451734.0</v>
+      </c>
+      <c r="M26" s="13"/>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>2616380.0</v>
+        <v>6098407.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1979,54 +1969,54 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25TLN</t>
+          <t>C25TSN</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>933</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3602750365</t>
+          <t>3502425026</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CỒN - LÊ NGUYỄN</t>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>A2/189 B, KP 2, Phường Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3501844024</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>4254640.0</v>
+        <v>9823789.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>340371.0</v>
+        <v>785903.0</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>4595011.0</v>
+        <v>1.0609692E7</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2044,6 +2034,1150 @@
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TSN</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502425026</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>1.742187E7</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>1393750.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>1.881562E7</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TSN</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502425026</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>3486902.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>278952.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>3765854.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TSN</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>27/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502425026</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỮU THỨC SUỐI NGHỆ</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Hữu Phước, Xã Ngãi Giao, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>1.2959976E7</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>1036798.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>1.3996774E7</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TTT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502443949</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ THƯƠNG TRƯỜNG</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 132 Đường Huyền Trân Công Chúa, Phường Tam Thắng, Thành phố  Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>3194444.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>255556.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>3450000.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TYM</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>8947</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3600359036</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN GẠCH MEN Ý MỸ</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Khu Công Nghiệp Tam Phước, Quốc Lộ 51, Phường Tam Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>1496304.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>119704.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>1616008.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TYM</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3600359036</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN GẠCH MEN Ý MỸ</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Khu Công Nghiệp Tam Phước, Quốc Lộ 51, Phường Tam Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>187038.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>14963.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>202001.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>4696</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3602212751</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ TRANG HOÀNG PHƯƠNG</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 1811, Quốc lộ 51, ấp Hiền Hòa, Xã Phước Thái, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>9.2592593E7</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>7407407.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>1.0E8</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>28/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3602212751</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ TRANG HOÀNG PHƯƠNG</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 1811, Quốc lộ 51, ấp Hiền Hòa, Xã Phước Thái, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>9.2592593E7</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>7407407.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>1.0E8</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3603155640</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TRANG HẬU PHƯƠNG</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 230A, tổ 4, ấp Hiền Hòa, Xã Phước Thái,Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>4.4028445E7</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>3522275.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>4.755072E7</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25TDP</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3603488840</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NAM ĐỒNG PHÁT</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 251, tổ 5, khu phố Tân Cang, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÔNG DƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1.9360185E7</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>1548815.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>2.0909E7</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25TBH</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>5200898982-006</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Đồng Nai - Công Ty Cổ Phần Gạch Ốp Lát Hoà Bình Minh</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>A25, Khu phố 5, Phường Tam Hiệp, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đông Dương Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>5543585.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>443487.0</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>5987072.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25TBH</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>5200898982-006</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Đồng Nai - Công Ty Cổ Phần Gạch Ốp Lát Hoà Bình Minh</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>A25, Khu phố 5, Phường Tam Hiệp, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đông Dương Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>1.0283367E7</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>822669.0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>1.1106036E7</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25TBH</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>5200898982-006</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Đồng Nai - Công Ty Cổ Phần Gạch Ốp Lát Hoà Bình Minh</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>A25, Khu phố 5, Phường Tam Hiệp, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đông Dương Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>3.447711E7</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>2758169.0</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>3.7235279E7</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25TBH</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>5200898982-006</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Chi Nhánh Đồng Nai - Công Ty Cổ Phần Gạch Ốp Lát Hoà Bình Minh</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>A25, Khu phố 5, Phường Tam Hiệp, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3501844024</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH Đông Dương Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>4449340.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>355947.0</v>
+      </c>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>4805287.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
